--- a/assets/forms/F14_나이스평가계획업로드작성도우미_작성예시_5학년SW.xlsx
+++ b/assets/forms/F14_나이스평가계획업로드작성도우미_작성예시_5학년SW.xlsx
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>산출물 분석(점검표·자료 카드 분류·작품 설명 카드), 구술 확인, ※ ‘끝까지 해결하려는 태도’는 이 차시 한 번이 아니라 21~32차시 개인 기록지(고치고 다시 시험한 기록)를 누적 관찰해 따로 평가함</t>
+          <t>산출물 분석(점검표·자료 카드 분류·작품 설명 카드), 구술 확인, ※ ‘끝까지 해결하려는 태도’는 성취기준 밖이므로 평가에 넣지 않고, 21∼32차시 개인 기록지(고치고 다시 시험한 기록)로 참여를 관찰해 기록만 함(세특 참고)</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
